--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.127.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.127.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.127" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.127" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.127.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.127.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0127.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0127.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -835,7 +835,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.127.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.127.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.127" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.127" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -601,28 +601,36 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L8: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN | isolated marker/symbol line :: å®¶</t>
+          <t>L8: stray/suspicious non-ASCII glyph(s): U+5BB6 CJK UNIFIED IDEOGRAPH-5BB6 | isolated marker/symbol line :: 家</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: respondent respectively.â€”Provided always, that nothing</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]120</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]120</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 120</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]120</t>
+        </is>
+      </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L92: line starts with punctuation glued to text :: .absence, of t</t>
+          <t>L16: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •the Statute twelfth Victoria, Chapter sixty-three, Section</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -645,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -660,26 +668,30 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢the Statute twelfth Victoria, Chapter sixty-three, Section</t>
+          <t>L16: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •the Statute twelfth Victoria, Chapter sixty-three, Section</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L8: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN | isolated marker/symbol line :: å®¶</t>
+          <t>L8: stray/suspicious non-ASCII glyph(s): U+5BB6 CJK UNIFIED IDEOGRAPH-5BB6 | isolated marker/symbol line :: 家</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr"/>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •costs and damages as shall be awarded in case the judg-</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -711,26 +723,30 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN | isolated marker/symbol line :: å®¶</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | isolated marker/symbol line :: ）</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢costs and damages as shall be awarded in case the judg-</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •costs and damages as shall be awarded in case the judg-</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr"/>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L92: line starts with punctuation glued to text :: .absence, of t</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -746,12 +762,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -762,14 +778,10 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tyâ€™s Court of</t>
-        </is>
-      </c>
+          <t>L76: stray/suspicious non-ASCII glyph(s): U+5BB6 CJK UNIFIED IDEOGRAPH-5BB6 | isolated marker/symbol line :: 家</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -811,7 +823,11 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr"/>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>L81: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
@@ -854,13 +870,17 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr"/>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>L171: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | isolated marker/symbol line :: ）</t>
+        </is>
+      </c>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L64: isolated marker/symbol line :: 120</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | isolated marker/symbol line :: ）</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -903,7 +923,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN | isolated marker/symbol line :: å®¶</t>
+          <t>L64: isolated marker/symbol line :: 120</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -946,7 +966,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L76: stray/suspicious non-ASCII glyph(s): U+5BB6 CJK UNIFIED IDEOGRAPH-5BB6 | isolated marker/symbol line :: 家</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -969,12 +989,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -989,7 +1009,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: V</t>
+          <t>L81: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1017,7 +1037,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1032,7 +1052,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L169: isolated marker/symbol line :: v</t>
+          <t>L91: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1055,12 +1075,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1073,7 +1093,11 @@
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>L169: isolated marker/symbol line :: v</t>
+        </is>
+      </c>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
@@ -1112,7 +1136,11 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L171: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | isolated marker/symbol line :: ）</t>
+        </is>
+      </c>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
@@ -1138,7 +1166,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
